--- a/data/trans_dic/P1401-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1401-Edad-trans_dic.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,3</t>
+          <t>0,13; 1,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,63</t>
+          <t>0,07; 0,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,78</t>
+          <t>0,28; 1,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,84</t>
+          <t>0,64; 2,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,64</t>
+          <t>0,66; 2,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,72</t>
+          <t>0,38; 1,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,83</t>
+          <t>0,62; 1,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,43</t>
+          <t>0,4; 1,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,32</t>
+          <t>0,28; 1,17</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,96</t>
+          <t>0,34; 2,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,04</t>
+          <t>0,33; 2,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,1</t>
+          <t>0,67; 2,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,16</t>
+          <t>1,92; 5,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,65</t>
+          <t>1,23; 3,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,59</t>
+          <t>1,83; 3,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,14</t>
+          <t>1,27; 3,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,4</t>
+          <t>0,97; 2,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,37</t>
+          <t>1,44; 2,75</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,33</t>
+          <t>0,71; 3,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,34</t>
+          <t>0,41; 2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,3</t>
+          <t>2,19; 5,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,84</t>
+          <t>2,73; 6,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,46</t>
+          <t>1,54; 4,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,72</t>
+          <t>2,43; 4,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,45</t>
+          <t>2,12; 4,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,98</t>
+          <t>1,12; 2,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,65</t>
+          <t>2,6; 4,47</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,11</t>
+          <t>1,9; 6,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,72</t>
+          <t>0,85; 3,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,13</t>
+          <t>3,0; 6,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,5</t>
+          <t>1,76; 5,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,57</t>
+          <t>3,01; 7,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,07</t>
+          <t>3,36; 6,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,42</t>
+          <t>2,13; 5,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,87</t>
+          <t>2,19; 5,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,78</t>
+          <t>3,48; 5,72</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,77</t>
+          <t>1,24; 5,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,44</t>
+          <t>2,39; 7,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 9,31</t>
+          <t>4,92; 9,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,7</t>
+          <t>1,14; 4,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,44</t>
+          <t>1,85; 6,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,74</t>
+          <t>2,92; 5,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,23</t>
+          <t>1,54; 4,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,86</t>
+          <t>2,6; 6,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,46</t>
+          <t>4,05; 6,76</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,55</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,22</t>
+          <t>0,62; 1,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,48</t>
+          <t>1,65; 2,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,64</t>
+          <t>1,54; 2,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,67</t>
+          <t>1,51; 2,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,55</t>
+          <t>1,91; 2,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,94</t>
+          <t>1,31; 1,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,76</t>
+          <t>1,2; 1,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,4</t>
+          <t>1,94; 2,5</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>975</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2795</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>897; 8950</t>
+          <t>891; 8232</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8519</t>
+          <t>0; 10374</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1933,27 +1933,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4924</t>
+          <t>0; 5522</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4660</t>
+          <t>0; 4515</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>893; 8164</t>
+          <t>896; 8263</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4892</t>
+          <t>0; 5424</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9050</t>
+          <t>0; 13465</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7715</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1920; 12107</t>
+          <t>1921; 11591</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>0; 4677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8038</t>
+          <t>0; 10028</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4578; 20150</t>
+          <t>4565; 20295</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4356; 17493</t>
+          <t>4395; 18639</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1977; 9346</t>
+          <t>2366; 10600</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8073; 25527</t>
+          <t>8659; 25671</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5346; 18970</t>
+          <t>5384; 19419</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3425; 14190</t>
+          <t>3509; 14576</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>28728</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2078; 12056</t>
+          <t>2063; 12758</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2574; 13203</t>
+          <t>2121; 12979</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2761; 18569</t>
+          <t>4670; 17733</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11347; 31710</t>
+          <t>11805; 32247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7707; 23703</t>
+          <t>7966; 23402</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12038; 25573</t>
+          <t>13497; 27446</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15653; 38553</t>
+          <t>15595; 37693</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12388; 31092</t>
+          <t>12585; 31477</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15253; 37864</t>
+          <t>20611; 39377</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>20462</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39104</t>
+          <t>41452</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3123; 14300</t>
+          <t>3067; 14388</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1984; 11178</t>
+          <t>1937; 10977</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12663; 29663</t>
+          <t>13313; 31800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12531; 30624</t>
+          <t>12245; 29849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6839; 22183</t>
+          <t>7642; 22455</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13492; 25621</t>
+          <t>14706; 27721</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17134; 39036</t>
+          <t>18603; 38730</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11430; 29026</t>
+          <t>10878; 28229</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30336; 51223</t>
+          <t>31576; 54257</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>17677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>37846</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5089; 22037</t>
+          <t>5873; 21130</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2055; 12454</t>
+          <t>2827; 12874</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10506; 22482</t>
+          <t>12159; 26394</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5972; 19487</t>
+          <t>6222; 19600</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11303; 28584</t>
+          <t>11383; 28298</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6533; 30852</t>
+          <t>14737; 27824</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15053; 35950</t>
+          <t>14159; 34843</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16249; 34661</t>
+          <t>15600; 35997</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17813; 46580</t>
+          <t>29362; 48283</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>21834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>18955</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>36528</t>
+          <t>40789</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3141; 14418</t>
+          <t>3105; 13547</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6552; 19114</t>
+          <t>6138; 19381</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13258; 26246</t>
+          <t>15228; 30714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5328; 18288</t>
+          <t>4433; 18168</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7021; 25781</t>
+          <t>7394; 26790</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12406; 24415</t>
+          <t>13563; 25946</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10488; 27030</t>
+          <t>9870; 25921</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16283; 38540</t>
+          <t>17084; 40838</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28219; 45691</t>
+          <t>31329; 52282</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>159325</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>27339; 53228</t>
+          <t>28645; 54935</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20040; 41430</t>
+          <t>21201; 42386</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52962; 85695</t>
+          <t>58261; 90426</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>56327; 93964</t>
+          <t>54850; 88816</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>55106; 94528</t>
+          <t>53433; 90386</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>60692; 93196</t>
+          <t>71138; 98188</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>89974; 135408</t>
+          <t>91287; 134369</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>82250; 122264</t>
+          <t>82952; 123352</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>123640; 170753</t>
+          <t>140385; 181701</t>
         </is>
       </c>
     </row>
